--- a/basedatos_partidas/salida/descompuestos/DRT010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/DRT010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H21"/>
+  <dimension ref="A3:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -464,14 +464,14 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Demolición de cielo raso y su estructura de soporte.</t>
+          <t>Demolición de cielo raso de yeso laminado y su estructura.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demolición de cielo raso existente de yeso, machihembrado o placa, junto con su estructura de soporte y elementos de cuelgue, con medios manuales. Incluye desconexión previa de las luminarias y elementos alojados en el plano del cielo, protección del piso y del mobiliario, retirada de escombro en sacos hasta el punto de acopio y limpieza de la zona, dejando la losa a la vista. No incluye el transporte a vertedero. Medido en superficie realmente demolida.
+          <t xml:space="preserve">Demolición de cielo raso continuo de placa de yeso laminado, junto con la perfilería de acero galvanizado, las varillas de cuelgue y el ángulo perimetral, ejecutada con medios manuales. Incluye la desconexión y retiro previo de las luminarias, rejillas y difusores alojados en el plano del cielo, la protección del piso y del mobiliario, el descuelgue ordenado de las placas para evitar caídas incontroladas, el retiro del escombro en sacos y de la perfilería atada, y la limpieza de la zona dejando la losa a la vista. No incluye el bote del escombro, que se valora en el capítulo de gestión de residuos. Medido en superficie realmente demolida.
 </t>
         </is>
       </c>
@@ -536,188 +536,266 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
         <v>0.65</v>
       </c>
       <c r="H10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="11">
-      <c r="F11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MT-CONS-DEM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Consumibles de demolición: puntas y cinceles de martillo, discos de corte y hojas de espátula.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MT-PROT-OBRA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Protección de obra con plástico, cartón corrugado y cinta de enmascarar.</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>Subtotal materiales:</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="H13" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>Equipo y maquinaria</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>MQ-ASPIR</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Aspirador industrial con filtro de polvo fino para limpieza de soporte y control de polvo.</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F15" t="n">
         <v>0.08</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G15" t="n">
         <v>2.1</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H15" t="n">
         <v>0.17</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal equipo y maquinaria:</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>Mano de obra</t>
-        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>MQ-ANDAMIO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Andamio tubular o de borriquetas para trabajos en altura, incluido montaje y desmontaje amortizados.</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal equipo y maquinaria:</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>Mano de obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>MO-AYU-ESP</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Ayudante especializado.</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MO-AYU</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Ayudante.</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>0.16</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal mano de obra:</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MO-AYU</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Ayudante.</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal mano de obra:</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="D20" t="inlineStr">
+    <row r="23">
+      <c r="D23" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H20" t="n">
+      <c r="G23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H23" t="n">
         <v>0.02</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Costes directos (1+2+3+4):</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="5" t="n">
-        <v>1.82</v>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="5" t="n">
+        <v>2.07</v>
       </c>
     </row>
   </sheetData>
